--- a/Iceberg_Schema_Evolution_History_load_Sample_data.xlsx
+++ b/Iceberg_Schema_Evolution_History_load_Sample_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maathu/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C30FE5FC-E128-8B42-9680-635794C0E62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A98C16C-D3A9-F14E-89A1-1B04854292F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{8E2CAB2B-2626-0447-9DE0-2675516F95F3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17720" xr2:uid="{8E2CAB2B-2626-0447-9DE0-2675516F95F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="27">
   <si>
     <t>id</t>
   </si>
@@ -127,9 +127,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -150,6 +150,30 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF633806"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF27500A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -187,23 +211,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -540,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63AC61C7-9E4B-E649-8623-7B5C6E4A8A96}">
-  <dimension ref="A2:S41"/>
+  <dimension ref="A2:S51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.1640625" bestFit="1" customWidth="1"/>
@@ -1099,10 +1136,10 @@
       <c r="G22" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1366,7 +1403,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33" s="2">
         <v>114</v>
       </c>
@@ -1392,7 +1429,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34" s="2">
         <v>114</v>
       </c>
@@ -1418,7 +1455,264 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="2:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B44" s="7">
+        <v>1</v>
+      </c>
+      <c r="C44" s="8">
+        <v>101</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="3">
+        <v>43423</v>
+      </c>
+      <c r="G44" s="3">
+        <v>44467</v>
+      </c>
+      <c r="H44" s="9">
+        <v>0</v>
+      </c>
+      <c r="I44" s="10">
+        <v>14000</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B45" s="7">
+        <v>2</v>
+      </c>
+      <c r="C45" s="8">
+        <v>101</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="3">
+        <v>44467</v>
+      </c>
+      <c r="G45" s="3">
+        <v>44970</v>
+      </c>
+      <c r="H45" s="9">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10">
+        <v>15000</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B46" s="7">
+        <v>3</v>
+      </c>
+      <c r="C46" s="8">
+        <v>101</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="3">
+        <v>44970</v>
+      </c>
+      <c r="G46" s="3">
+        <v>44998</v>
+      </c>
+      <c r="H46" s="9">
+        <v>0</v>
+      </c>
+      <c r="I46" s="10">
+        <v>15000</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B47" s="7">
+        <v>4</v>
+      </c>
+      <c r="C47" s="8">
+        <v>101</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="3">
+        <v>44998</v>
+      </c>
+      <c r="G47" s="3">
+        <v>45155</v>
+      </c>
+      <c r="H47" s="9">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10">
+        <v>15000</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B48" s="7">
+        <v>5</v>
+      </c>
+      <c r="C48" s="8">
+        <v>101</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
+        <v>45155</v>
+      </c>
+      <c r="G48" s="3">
+        <v>45165</v>
+      </c>
+      <c r="H48" s="9">
+        <v>0</v>
+      </c>
+      <c r="I48" s="10">
+        <v>17000</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B49" s="7">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>101</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3">
+        <v>45165</v>
+      </c>
+      <c r="G49" s="3">
+        <v>46102</v>
+      </c>
+      <c r="H49" s="9">
+        <v>0</v>
+      </c>
+      <c r="I49" s="10">
+        <v>17000</v>
+      </c>
+      <c r="J49" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B50" s="7">
+        <v>7</v>
+      </c>
+      <c r="C50" s="8">
+        <v>101</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="3">
+        <v>46102</v>
+      </c>
+      <c r="G50" s="3">
+        <v>46129</v>
+      </c>
+      <c r="H50" s="9">
+        <v>0</v>
+      </c>
+      <c r="I50" s="10">
+        <v>20000</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B51" s="7">
+        <v>8</v>
+      </c>
+      <c r="C51" s="8">
+        <v>101</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" s="3">
+        <v>46129</v>
+      </c>
+      <c r="G51" s="3">
+        <v>584389</v>
+      </c>
+      <c r="H51" s="12">
+        <v>1</v>
+      </c>
+      <c r="I51" s="10">
+        <v>20000</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
